--- a/Documenti/WorkInProgress.xlsx
+++ b/Documenti/WorkInProgress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Fattibilit-ODP\Documenti\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://divimast-my.sharepoint.com/personal/mattia_mille_divimast_it/Documents/Desktop/MM/Business Central/Fattibilit-ODP/Documenti/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59083F2-D5AB-4846-B08E-8FBF6F98D8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D59083F2-D5AB-4846-B08E-8FBF6F98D8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E8E94F9-693C-4FF6-9AD1-15CB5DD1CB33}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">Verificare fattibilità Z211248 articolo 2308861041	</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>Note</t>
+  </si>
+  <si>
+    <t>Risolto MM 03/02/2026</t>
   </si>
 </sst>
 </file>
@@ -69,12 +72,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -89,10 +98,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -374,14 +384,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="58.85546875" customWidth="1"/>
-    <col min="4" max="4" width="51.140625" customWidth="1"/>
+    <col min="1" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="58.88671875" customWidth="1"/>
+    <col min="4" max="4" width="51.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -398,7 +408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46055</v>
       </c>
@@ -407,6 +417,9 @@
       </c>
       <c r="C2" t="s">
         <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Documenti/WorkInProgress.xlsx
+++ b/Documenti/WorkInProgress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://divimast-my.sharepoint.com/personal/mattia_mille_divimast_it/Documents/Desktop/MM/Business Central/Fattibilit-ODP/Documenti/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Fattibilit-ODP\Documenti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D59083F2-D5AB-4846-B08E-8FBF6F98D8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E8E94F9-693C-4FF6-9AD1-15CB5DD1CB33}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B114CF-E46A-42DC-B3C6-944063E5DF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t xml:space="preserve">Verificare fattibilità Z211248 articolo 2308861041	</t>
   </si>
@@ -49,6 +49,36 @@
   </si>
   <si>
     <t>Risolto MM 03/02/2026</t>
+  </si>
+  <si>
+    <t>AL posto di Terzista --&gt; Area Produzione</t>
+  </si>
+  <si>
+    <t>Escludere Ordini Acq con Ord produzione</t>
+  </si>
+  <si>
+    <t>Aggiugere dopo Expected Tipo numero data 1o elemento</t>
+  </si>
+  <si>
+    <t>Se più di un elemento evidenzare (grassetto?)</t>
+  </si>
+  <si>
+    <t>Aggiungere richiamo monitor avanzamento ovunque c'è in ODP</t>
+  </si>
+  <si>
+    <t>Filtro Tutti solo esterni Solo interni</t>
+  </si>
+  <si>
+    <t>In prima lsta aggiungere codice cliente e nome cliente (ed anche nellultima)</t>
+  </si>
+  <si>
+    <t>Aggiungere filtro Linea produzione e grandezza (flowfield 5406)</t>
+  </si>
+  <si>
+    <t>Evicenziare fattibili in toto da fattibili con trasferimenti</t>
+  </si>
+  <si>
+    <t>Aggiungere campo Exterlan inventory Other Location su 2a lista</t>
   </si>
 </sst>
 </file>
@@ -98,11 +128,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -383,15 +414,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.5546875" customWidth="1"/>
-    <col min="3" max="3" width="58.88671875" customWidth="1"/>
-    <col min="4" max="4" width="51.109375" customWidth="1"/>
+    <col min="1" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="58.85546875" customWidth="1"/>
+    <col min="4" max="4" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -408,7 +439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46055</v>
       </c>
@@ -420,6 +451,116 @@
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Documenti/WorkInProgress.xlsx
+++ b/Documenti/WorkInProgress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Fattibilit-ODP\Documenti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B114CF-E46A-42DC-B3C6-944063E5DF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079EE97F-2305-40E1-8D52-054891CF3290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t xml:space="preserve">Verificare fattibilità Z211248 articolo 2308861041	</t>
   </si>
@@ -79,6 +79,18 @@
   </si>
   <si>
     <t>Aggiungere campo Exterlan inventory Other Location su 2a lista</t>
+  </si>
+  <si>
+    <t>in list 2 aggiungere Replanishment sistem e Planner</t>
+  </si>
+  <si>
+    <t>aggiungere avanzamento in Prod. Order Line List (5406, List)</t>
+  </si>
+  <si>
+    <t>Aggiungere campo data ordinemento (anche t 5406) e mettere la data di scadenza non più editabile. Se data ordinamento vuota in t 5406 nel temporaneo nella data ordinamento inserisco la data di scadenza.</t>
+  </si>
+  <si>
+    <t>aggiungere possibilità di inserire ordini simulati. Fare tipo azione che apre lista ordini simulati e scegli quali prendere in considerazione (mettere magari anche campo che ti dice il numero di simulati scelti). Con il carica dati considerare anche il simulato come se fosse un rilasciato (quindi NON metterli in fondo come i confermati).</t>
   </si>
 </sst>
 </file>
@@ -128,12 +140,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -414,11 +431,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="58.85546875" customWidth="1"/>
+    <col min="3" max="3" width="58.85546875" style="5" customWidth="1"/>
     <col min="4" max="4" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -429,7 +446,7 @@
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -446,7 +463,7 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -460,18 +477,18 @@
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46070</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -482,7 +499,7 @@
       <c r="B6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -493,7 +510,7 @@
       <c r="B7" t="s">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -504,7 +521,7 @@
       <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -515,7 +532,7 @@
       <c r="B9" t="s">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -526,7 +543,7 @@
       <c r="B10" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -537,7 +554,7 @@
       <c r="B11" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -548,7 +565,7 @@
       <c r="B12" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -559,8 +576,52 @@
       <c r="B13" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
